--- a/covid19_cases_switzerland.xlsx
+++ b/covid19_cases_switzerland.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daenu\Code\covid19-cases-switzerland\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sam/Documents/GitHub/covid19-cases-switzerland/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC8AFBD-944C-49C7-8E69-3B21F28DCFB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA5DC50-C154-BD47-B560-4AE9EBF6E122}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="2235" windowWidth="22290" windowHeight="17775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="820" yWindow="2240" windowWidth="22300" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="covid19_cases_switzerland" sheetId="1" r:id="rId1"/>
@@ -19,18 +19,10 @@
     <sheet name="Tests" sheetId="5" r:id="rId4"/>
     <sheet name="demographics" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -568,13 +560,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB19"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -660,7 +652,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>43896</v>
       </c>
@@ -748,7 +740,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>43897</v>
       </c>
@@ -836,7 +828,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>43898</v>
       </c>
@@ -924,7 +916,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>43899</v>
       </c>
@@ -1012,7 +1004,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>43900</v>
       </c>
@@ -1100,7 +1092,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>43901</v>
       </c>
@@ -1188,7 +1180,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>43902</v>
       </c>
@@ -1276,7 +1268,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>43903</v>
       </c>
@@ -1364,7 +1356,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>43904</v>
       </c>
@@ -1452,7 +1444,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>43905</v>
       </c>
@@ -1470,7 +1462,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>43906</v>
       </c>
@@ -1512,7 +1504,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>43907</v>
       </c>
@@ -1560,7 +1552,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>43908</v>
       </c>
@@ -1648,7 +1640,7 @@
         <v>3674</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>43909</v>
       </c>
@@ -1736,7 +1728,7 @@
         <v>4954</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>43910</v>
       </c>
@@ -1823,7 +1815,7 @@
         <v>6249</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>43911</v>
       </c>
@@ -1904,7 +1896,7 @@
         <v>7220</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>43912</v>
       </c>
@@ -1979,7 +1971,7 @@
         <v>7741</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>43913</v>
       </c>
@@ -1991,6 +1983,9 @@
       </c>
       <c r="Q19">
         <v>185</v>
+      </c>
+      <c r="R19">
+        <v>30</v>
       </c>
       <c r="AB19" s="4">
         <f>AB18+Q19-Q18+K19-K18+E19-E17</f>
@@ -1998,7 +1993,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="U5:U17">
+  <sortState ref="U5:U17">
     <sortCondition ref="U5"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2009,33 +2004,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57F7F9FF-DA82-4772-9651-CE094ADEC3E5}">
   <dimension ref="A1:AB19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.5" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -2121,7 +2116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>43896</v>
       </c>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="AB2" s="4"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>43897</v>
       </c>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB3" s="4"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>43898</v>
       </c>
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB4" s="4"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>43899</v>
       </c>
@@ -2181,7 +2176,7 @@
       </c>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>43900</v>
       </c>
@@ -2196,7 +2191,7 @@
       </c>
       <c r="AB6" s="4"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>43901</v>
       </c>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="AB7" s="4"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>43902</v>
       </c>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="AB8" s="4"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>43903</v>
       </c>
@@ -2247,7 +2242,7 @@
       </c>
       <c r="AB9" s="4"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>43904</v>
       </c>
@@ -2265,7 +2260,7 @@
       </c>
       <c r="AB10" s="4"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>43905</v>
       </c>
@@ -2289,7 +2284,7 @@
       </c>
       <c r="AB11" s="4"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>43906</v>
       </c>
@@ -2316,7 +2311,7 @@
       </c>
       <c r="AB12" s="5"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>43907</v>
       </c>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="AB13" s="4"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>43908</v>
       </c>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AB14" s="4"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>43909</v>
       </c>
@@ -2381,7 +2376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>43910</v>
       </c>
@@ -2414,7 +2409,7 @@
       </c>
       <c r="AB16" s="4"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>43911</v>
       </c>
@@ -2462,7 +2457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>43912</v>
       </c>
@@ -2510,7 +2505,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>43913</v>
       </c>
@@ -2566,18 +2561,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B7CD16-821B-4F71-9E45-F399140EBC9C}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="180.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="2" max="2" width="180.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2585,7 +2580,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2593,7 +2588,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2601,7 +2596,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2612,7 +2607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2623,7 +2618,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2634,7 +2629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2642,7 +2637,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2653,7 +2648,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2664,7 +2659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2675,7 +2670,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -2684,7 +2679,7 @@
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2695,7 +2690,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2709,7 +2704,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2720,7 +2715,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2728,7 +2723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2739,7 +2734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2750,7 +2745,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2758,7 +2753,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2766,7 +2761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2805,13 +2800,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB15D9C-377E-4F66-998B-5427F83AE200}">
   <dimension ref="A1:AB13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -2897,73 +2892,73 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>43896</v>
       </c>
       <c r="AB2" s="4"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>43897</v>
       </c>
       <c r="AB3" s="4"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>43898</v>
       </c>
       <c r="AB4" s="4"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>43899</v>
       </c>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>43900</v>
       </c>
       <c r="AB6" s="4"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>43901</v>
       </c>
       <c r="AB7" s="4"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>43902</v>
       </c>
       <c r="AB8" s="4"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>43903</v>
       </c>
       <c r="AB9" s="4"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>43904</v>
       </c>
       <c r="AB10" s="4"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>43905</v>
       </c>
       <c r="AB11" s="4"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>43906</v>
       </c>
       <c r="AB12" s="5"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>43907</v>
       </c>
@@ -2980,13 +2975,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31030D7-6127-45B4-88E3-D01E088D3FDA}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -3009,7 +3004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3051,7 +3046,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3093,7 +3088,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3135,7 +3130,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3177,7 +3172,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3219,7 +3214,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -3261,7 +3256,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -3303,7 +3298,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3345,7 +3340,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3387,7 +3382,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3429,7 +3424,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3471,7 +3466,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3513,7 +3508,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3555,7 +3550,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -3597,7 +3592,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -3639,7 +3634,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -3681,7 +3676,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -3723,7 +3718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -3765,7 +3760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -3807,7 +3802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -3849,7 +3844,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -3891,7 +3886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -3933,7 +3928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -3975,7 +3970,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -4017,7 +4012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -4059,7 +4054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -4101,7 +4096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
